--- a/home/src/site_apps/central/data/Material_Inventory.xlsx
+++ b/home/src/site_apps/central/data/Material_Inventory.xlsx
@@ -27309,25 +27309,25 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>9441641</v>
+        <v>13575105</v>
       </c>
       <c r="N2" t="n">
-        <v>9441641</v>
+        <v>13575105</v>
       </c>
       <c r="O2" t="n">
-        <v>2615334</v>
+        <v>3268210</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>707019</v>
+        <v>1722002</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>6119288</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
@@ -27338,7 +27338,7 @@
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
-          <t>{"\uc774\uc0ac": {"personnel": "", "period": "", "unit_price": 230208.33333333334}, "\ubd80\uc7a5": {"personnel": "2", "period": "4.5", "unit_price": 230208.33333333334}, "\ucc28\uc7a5": {"personnel": "", "period": "", "unit_price": 198625.0}, "\uacfc\uc7a5": {"personnel": "", "period": "", "unit_price": 171541.66666666666}, "\ub300\ub9ac": {"personnel": "", "period": "", "unit_price": 158000.0}, "\uacc4\uc7a5": {"personnel": "1", "period": "1", "unit_price": 144458.33333333334}, "\uc8fc\uc784": {"personnel": "", "period": "", "unit_price": 130916.66666666667}, "\uae30\uc0ac": {"personnel": "", "period": "", "unit_price": 121875.0}, "\uc5f0\uc7a5\uadfc\ubb34": {"personnel": "2", "period": "3", "unit_price": 4000.0}, "\uc57c\uac04\uadfc\ubb34": {"personnel": "", "period": "", "unit_price": 5000.0}, "\ud734\uc77c\uadfc\ubb34": {"personnel": "3", "period": "16.6667", "unit_price": 7500.0}}</t>
+          <t>{"\uc774\uc0ac": {"personnel": "", "period": "", "unit_price": 230208.33333333334}, "\ubd80\uc7a5": {"personnel": "2", "period": "5.5", "unit_price": 230208.33333333334}, "\ucc28\uc7a5": {"personnel": "", "period": "", "unit_price": 198625.0}, "\uacfc\uc7a5": {"personnel": "", "period": "", "unit_price": 171541.66666666666}, "\ub300\ub9ac": {"personnel": "", "period": "", "unit_price": 158000.0}, "\uacc4\uc7a5": {"personnel": "1", "period": "2", "unit_price": 144458.33333333334}, "\uc8fc\uc784": {"personnel": "", "period": "", "unit_price": 130916.66666666667}, "\uae30\uc0ac": {"personnel": "", "period": "", "unit_price": 121875.0}, "\uc5f0\uc7a5\uadfc\ubb34": {"personnel": "3", "period": "6", "unit_price": 4000.0}, "\uc57c\uac04\uadfc\ubb34": {"personnel": "", "period": "", "unit_price": 5000.0}, "\ud734\uc77c\uadfc\ubb34": {"personnel": "3", "period": "16.6667", "unit_price": 7500.0}}</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>{"site_expense": [{"cat": "\ucc28\ub7c9\uc720\uc9c0\ube44", "cont": "\uc8fc\uc720, \uc218\ub9ac, \ud1b5\ud589, \uc8fc\ucc28 \ub4f1", "ppl": "N/A", "qty": "6", "unit": "\uc77c", "price": "6667", "amount": "40,002"}, {"cat": "\uc18c\ubaa8\ud488\ube44", "cont": "\uc7a5\uac11,\uc77c\ud68c\uc6a9 \uc791\uc5c5\ubcf5\uc678", "ppl": "N/A", "qty": "6", "unit": "\uc77c", "price": "3333", "amount": "19,998"}, {"cat": "\ubcf5\ub9ac\ud6c4\uc0dd\ube44", "cont": "\uc0dd\uc218, \uc74c\ub8cc \uc678 \uae30\ud0c0", "ppl": "N/A", "qty": "6", "unit": "\uc77c", "price": "1667", "amount": "10,002"}, {"cat": "Se-175", "cont": "\ubc29\uc0ac\uc131\ub3d9\uc704\uc6d0\uc18c \uad6c\ub9e4", "ppl": "N/A", "qty": "", "unit": "\uc77c", "price": "35,714", "amount": "0"}], "rental": [{"cat": "", "spec": "", "qty": "", "period": "", "unit": "", "price": "0", "amount": "0"}, {"cat": "", "spec": "", "qty": "", "period": "", "unit": "", "price": "0", "amount": "0"}, {"cat": "", "spec": "", "qty": "", "period": "", "unit": "", "price": "0", "amount": "0"}], "outsource": [{"cat": "\ucf00\uc774\uc5d4\ub514\uc774", "work": "\ubc29\uc0ac\uc120\ud22c\uacfc\uac80\uc0ac", "count": "0", "price": "0", "amount": "0"}, {"cat": "", "work": "", "count": "0", "price": "0", "amount": "0"}, {"cat": "", "work": "", "count": "0", "price": "0", "amount": "0"}], "depreciation": [{"item": "PAUT \uc7a5\ube44", "spec": "", "life": "5", "qty": "1", "days": "5", "rate": "44,444", "amount": "222,222"}, {"item": "PAUT SCANNER (MANUAL)", "spec": "", "life": "5", "qty": "1", "days": "5", "rate": "5,556", "amount": "27,778"}, {"item": "PAUT SCANNER (COBRA)", "spec": "", "life": "5", "qty": "1", "days": "", "rate": "16,667", "amount": "0"}, {"item": "YOKE", "spec": "", "life": "5", "qty": "1", "days": "", "rate": "222", "amount": "0"}, {"item": "\ud604\uc0c1\uc6a9 \ud0d1\ucc28(5\ub144\uac04 \ubcf4\ud5d8\ube44 \ud3ec\ud568)", "spec": "\ud604\uc7a5\ubcc4 \ucc28\ub7c9\uae30\uc785\uc2dc \ud0d1\ucc28 \uad6c\ubd84 \uae30\uc785", "life": "5", "qty": "1", "days": "", "rate": "16,667", "amount": "0"}, {"item": "\uc2a4\ud0c0\ub809\uc2a4(5\ub144\uac04 \ubcf4\ud5d8\ube44 \ud3ec\ud568)", "spec": "\ud604\uc7a5\ubcc4 \ucc28\ub7c9\uae30\uc785\uc2dc \uc2a4\ud0c0\ub809\uc2a4 \uad6c\ubd84 \uae30\uc785", "life": "5", "qty": "1", "days": "6", "rate": "16,667", "amount": "100,000"}], "_depreciation_precise_rates": [44444.441666666666, 5555.558333333333, 16666.666666666668, 222.2, 16666.666666666668, 16666.66875]}</t>
+          <t>{"site_expense": [{"cat": "\ucc28\ub7c9\uc720\uc9c0\ube44", "cont": "\uc8fc\uc720, \uc218\ub9ac, \ud1b5\ud589, \uc8fc\ucc28 \ub4f1", "ppl": "4", "qty": "7", "unit": "\uc77c", "price": "6667", "amount": "46,669"}, {"cat": "\uc18c\ubaa8\ud488\ube44", "cont": "\uc7a5\uac11,\uc77c\ud68c\uc6a9 \uc791\uc5c5\ubcf5\uc678", "ppl": "N/A", "qty": "6", "unit": "\uac1c\uc6d4", "price": "100,000", "amount": "600,000"}, {"cat": "\ubcf5\ub9ac\ud6c4\uc0dd\ube44", "cont": "\uc0dd\uc218, \uc74c\ub8cc \uc678 \uae30\ud0c0", "ppl": "N/A", "qty": "6", "unit": "\uac1c\uc6d4", "price": "50,000", "amount": "300,000"}, {"cat": "Se-175", "cont": "\ubc29\uc0ac\uc131\ub3d9\uc704\uc6d0\uc18c \uad6c\ub9e4", "ppl": "N/A", "qty": "", "unit": "\uc77c", "price": "35,714", "amount": "0"}], "rental": [{"cat": "", "spec": "", "qty": "", "period": "", "unit": "", "price": "0", "amount": "0"}, {"cat": "", "spec": "", "qty": "", "period": "", "unit": "", "price": "0", "amount": "0"}, {"cat": "", "spec": "", "qty": "", "period": "", "unit": "", "price": "0", "amount": "0"}], "outsource": [{"cat": "\ucf00\uc774\uc5d4\ub514\uc774", "work": "\ubc29\uc0ac\uc120\ud22c\uacfc\uac80\uc0ac", "count": "0", "price": "0", "amount": "0"}, {"cat": "", "work": "", "count": "0", "price": "0", "amount": "0"}, {"cat": "", "work": "", "count": "0", "price": "0", "amount": "0"}], "depreciation": [{"item": "PAUT \uc7a5\ube44", "spec": "", "life": "5", "qty": "1", "days": "6", "rate": "44,444", "amount": "266,667"}, {"item": "PAUT SCANNER (MANUAL)", "spec": "", "life": "5", "qty": "1", "days": "6", "rate": "5,556", "amount": "33,333"}, {"item": "PAUT SCANNER (COBRA)", "spec": "", "life": "5", "qty": "1", "days": "", "rate": "16,667", "amount": "0"}, {"item": "YOKE", "spec": "", "life": "5", "qty": "1", "days": "", "rate": "222", "amount": "0"}, {"item": "\ud604\uc0c1\uc6a9 \ud0d1\ucc28(5\ub144\uac04 \ubcf4\ud5d8\ube44 \ud3ec\ud568)", "spec": "\ud604\uc7a5\ubcc4 \ucc28\ub7c9\uae30\uc785\uc2dc \ud0d1\ucc28 \uad6c\ubd84 \uae30\uc785", "life": "5", "qty": "1", "days": "", "rate": "16,667", "amount": "0"}, {"item": "\uc2a4\ud0c0\ub809\uc2a4(5\ub144\uac04 \ubcf4\ud5d8\ube44 \ud3ec\ud568)", "spec": "\ud604\uc7a5\ubcc4 \ucc28\ub7c9\uae30\uc785\uc2dc \uc2a4\ud0c0\ub809\uc2a4 \uad6c\ubd84 \uae30\uc785", "life": "5", "qty": "1", "days": "7", "rate": "16,667", "amount": "116,667"}], "_depreciation_precise_rates": [44444.441666666666, 5555.558333333333, 16666.666666666668, 222.2, 16666.666666666668, 16666.66875]}</t>
         </is>
       </c>
     </row>
@@ -27396,10 +27396,10 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>13461323</v>
+        <v>13575105</v>
       </c>
       <c r="N3" t="n">
-        <v>13461323</v>
+        <v>13575105</v>
       </c>
       <c r="O3" t="n">
         <v>3268210</v>

--- a/home/src/site_apps/central/data/Material_Inventory.xlsx
+++ b/home/src/site_apps/central/data/Material_Inventory.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Materials" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Budget" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Settings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24725,7 +24725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DE8"/>
+  <dimension ref="A1:DE11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27124,6 +27124,779 @@
         <v>0</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>중앙지사</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>480</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.0018</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" s="1" t="n">
+        <v>46284.57457754629</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>PAUT MX2(OMNI2-103085)</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>3.0018</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>201863</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>605952</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>PAUT</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>(주간) 09:00~18:00</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>95가0175 (스타렉스)</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:안함|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:안함</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>한국지역난방공사 중앙지사</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr"/>
+      <c r="BR9" t="inlineStr"/>
+      <c r="BS9" t="inlineStr"/>
+      <c r="BT9" t="inlineStr"/>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>Pipe</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>KS B ISO 13588</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr"/>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>300A 이상 (1.0)</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr"/>
+      <c r="CE9" t="inlineStr"/>
+      <c r="CF9" t="inlineStr"/>
+      <c r="CG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>3.0018</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>112744</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>195717</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>215289</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>82201</v>
+      </c>
+      <c r="CM9" t="inlineStr"/>
+      <c r="CN9" t="inlineStr"/>
+      <c r="CO9" t="inlineStr"/>
+      <c r="CP9" t="inlineStr"/>
+      <c r="CQ9" t="inlineStr"/>
+      <c r="CR9" t="inlineStr"/>
+      <c r="CS9" t="inlineStr"/>
+      <c r="CT9" t="inlineStr"/>
+      <c r="CU9" t="inlineStr"/>
+      <c r="CV9" t="inlineStr"/>
+      <c r="CW9" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="CX9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ9" t="inlineStr">
+        <is>
+          <t>300A</t>
+        </is>
+      </c>
+      <c r="DA9" t="inlineStr">
+        <is>
+          <t>열배관</t>
+        </is>
+      </c>
+      <c r="DB9" t="inlineStr"/>
+      <c r="DC9" t="inlineStr"/>
+      <c r="DD9" t="inlineStr"/>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>중앙지사</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>480</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11.0066</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" s="1" t="n">
+        <v>46284.57550633102</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>PAUT MX2(OMNI2-103085)</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>11.0066</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>201863</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2221825</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>PAUT</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>(주간) 09:00~22:00</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>차장 권인경</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>(주간) 09:00~22:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>95가0175 (스타렉스)</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:안함|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:안함</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>한국지역난방공사 중앙지사</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr"/>
+      <c r="BQ10" t="inlineStr"/>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="inlineStr"/>
+      <c r="BT10" t="inlineStr"/>
+      <c r="BU10" t="inlineStr"/>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>Pipe</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>KS B ISO 13588</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr"/>
+      <c r="BY10" t="inlineStr"/>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr"/>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>300A 이상 (1.0)</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr"/>
+      <c r="CE10" t="inlineStr"/>
+      <c r="CF10" t="inlineStr"/>
+      <c r="CG10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>11.0066</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>413396</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>717630</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>789393</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>301404</v>
+      </c>
+      <c r="CM10" t="inlineStr"/>
+      <c r="CN10" t="inlineStr"/>
+      <c r="CO10" t="inlineStr"/>
+      <c r="CP10" t="inlineStr"/>
+      <c r="CQ10" t="inlineStr"/>
+      <c r="CR10" t="inlineStr"/>
+      <c r="CS10" t="inlineStr"/>
+      <c r="CT10" t="inlineStr"/>
+      <c r="CU10" t="inlineStr"/>
+      <c r="CV10" t="inlineStr"/>
+      <c r="CW10" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="CX10" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ10" t="inlineStr">
+        <is>
+          <t>300A</t>
+        </is>
+      </c>
+      <c r="DA10" t="inlineStr">
+        <is>
+          <t>열배관</t>
+        </is>
+      </c>
+      <c r="DB10" t="inlineStr"/>
+      <c r="DC10" t="inlineStr"/>
+      <c r="DD10" t="inlineStr"/>
+      <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>중앙지사</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>480</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.436</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" s="1" t="n">
+        <v>46284.59910578703</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>PAUT MX2(OMNI2-103085)</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>5.436</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>257675</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1400721</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>PAUT</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>(주간) 09:00~22:00</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>차장 권인경</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>(주간) 09:00~22:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>95가0175 (스타렉스)</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:안함|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:안함</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>한국지역난방공사 중앙지사</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr"/>
+      <c r="BP11" t="inlineStr"/>
+      <c r="BQ11" t="inlineStr"/>
+      <c r="BR11" t="inlineStr"/>
+      <c r="BS11" t="inlineStr"/>
+      <c r="BT11" t="inlineStr"/>
+      <c r="BU11" t="inlineStr"/>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>Pipe</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>KS B ISO 13588</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr"/>
+      <c r="BY11" t="inlineStr"/>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr"/>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>200A (1.0)</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr"/>
+      <c r="CE11" t="inlineStr"/>
+      <c r="CF11" t="inlineStr"/>
+      <c r="CG11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>5.436</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>204170</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>474823</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>522301</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>199425</v>
+      </c>
+      <c r="CM11" t="inlineStr"/>
+      <c r="CN11" t="inlineStr"/>
+      <c r="CO11" t="inlineStr"/>
+      <c r="CP11" t="inlineStr"/>
+      <c r="CQ11" t="inlineStr"/>
+      <c r="CR11" t="inlineStr"/>
+      <c r="CS11" t="inlineStr"/>
+      <c r="CT11" t="inlineStr"/>
+      <c r="CU11" t="inlineStr"/>
+      <c r="CV11" t="inlineStr"/>
+      <c r="CW11" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="CX11" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ11" t="inlineStr">
+        <is>
+          <t>200A</t>
+        </is>
+      </c>
+      <c r="DA11" t="inlineStr">
+        <is>
+          <t>열배관</t>
+        </is>
+      </c>
+      <c r="DB11" t="inlineStr"/>
+      <c r="DC11" t="inlineStr"/>
+      <c r="DD11" t="inlineStr"/>
+      <c r="DE11" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/home/src/site_apps/central/data/Material_Inventory.xlsx
+++ b/home/src/site_apps/central/data/Material_Inventory.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Materials" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Budget" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Settings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S473"/>
+  <dimension ref="A1:S474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24529,6 +24529,59 @@
         <v>0</v>
       </c>
       <c r="S473" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>481</v>
+      </c>
+      <c r="B474" t="inlineStr"/>
+      <c r="C474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Carestream T200-3⅓*6"</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Carestream T200-3⅓*6"</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr"/>
+      <c r="I474" t="inlineStr"/>
+      <c r="J474" t="inlineStr"/>
+      <c r="K474" t="n">
+        <v>0</v>
+      </c>
+      <c r="L474" t="n">
+        <v>0</v>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="N474" t="inlineStr"/>
+      <c r="O474" t="inlineStr"/>
+      <c r="P474" t="inlineStr"/>
+      <c r="Q474" t="n">
+        <v>0</v>
+      </c>
+      <c r="R474" t="n">
+        <v>10</v>
+      </c>
+      <c r="S474" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24543,7 +24596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24662,6 +24715,69 @@
           <t>수량</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B2" t="n">
+        <v>481</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>중앙지사 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>부장 주진철, 부장 박광복</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>중앙지사</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>81두1580 (탑차)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24725,7 +24841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DE11"/>
+  <dimension ref="A1:DE12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27897,6 +28013,261 @@
         <v>0</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>중앙지사</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>481</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" s="1" t="n">
+        <v>46294.71757018519</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Se-75</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>138793</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>832758</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>(주간) 09:00~18:00</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>부장 박광복</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>(주간) 09:00~18:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>81두1580 (탑차)</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>한국지역난방공사 중앙지사</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr"/>
+      <c r="BP12" t="inlineStr"/>
+      <c r="BQ12" t="inlineStr"/>
+      <c r="BR12" t="inlineStr"/>
+      <c r="BS12" t="inlineStr"/>
+      <c r="BT12" t="inlineStr"/>
+      <c r="BU12" t="inlineStr"/>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>Pipe</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr"/>
+      <c r="BX12" t="inlineStr"/>
+      <c r="BY12" t="inlineStr"/>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr"/>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>Ir-192 또는 Se-75 (1.0)</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>15mm 이하 (1.0)</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr"/>
+      <c r="CF12" t="inlineStr"/>
+      <c r="CG12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>6</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>48264</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>311310</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>342438</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>130746</v>
+      </c>
+      <c r="CM12" t="inlineStr"/>
+      <c r="CN12" t="inlineStr"/>
+      <c r="CO12" t="inlineStr"/>
+      <c r="CP12" t="inlineStr"/>
+      <c r="CQ12" t="inlineStr"/>
+      <c r="CR12" t="inlineStr"/>
+      <c r="CS12" t="inlineStr"/>
+      <c r="CT12" t="inlineStr"/>
+      <c r="CU12" t="inlineStr"/>
+      <c r="CV12" t="inlineStr"/>
+      <c r="CW12" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="CX12" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ12" t="inlineStr">
+        <is>
+          <t>80A</t>
+        </is>
+      </c>
+      <c r="DA12" t="inlineStr">
+        <is>
+          <t>열수송관</t>
+        </is>
+      </c>
+      <c r="DB12" t="inlineStr"/>
+      <c r="DC12" t="inlineStr"/>
+      <c r="DD12" t="inlineStr"/>
+      <c r="DE12" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/home/src/site_apps/central/data/Material_Inventory.xlsx
+++ b/home/src/site_apps/central/data/Material_Inventory.xlsx
@@ -24841,7 +24841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DE12"/>
+  <dimension ref="A1:DE13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28268,6 +28268,273 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>중앙지사</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>480</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.1546</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" s="1" t="n">
+        <v>46301.46898743055</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>PAUT MX2(OMNI2-103085)</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>2.1546</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>270981</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>583855</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>PAUT</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>(휴일) 09:00~18:00</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>67,500</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>부장 이병국</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>(휴일) 09:00~18:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>67,500</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>90서8616 (스타렉스) || 개인차량(이병국부장)</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>60 ||</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:안함|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:안함 || out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:안함|in_exterior:양호</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>||</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>한국지역난방공사 중앙지사</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr"/>
+      <c r="BP13" t="inlineStr"/>
+      <c r="BQ13" t="inlineStr"/>
+      <c r="BR13" t="inlineStr"/>
+      <c r="BS13" t="inlineStr"/>
+      <c r="BT13" t="inlineStr"/>
+      <c r="BU13" t="inlineStr"/>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>Pipe</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr">
+        <is>
+          <t>KS B ISO 13588</t>
+        </is>
+      </c>
+      <c r="BX13" t="inlineStr"/>
+      <c r="BY13" t="inlineStr"/>
+      <c r="BZ13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr"/>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="CC13" t="inlineStr">
+        <is>
+          <t>100A 이하 (1.0)</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr"/>
+      <c r="CE13" t="inlineStr"/>
+      <c r="CF13" t="inlineStr"/>
+      <c r="CG13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>2.1546</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>82368</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>199003</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>218903</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>83581</v>
+      </c>
+      <c r="CM13" t="inlineStr"/>
+      <c r="CN13" t="inlineStr"/>
+      <c r="CO13" t="inlineStr"/>
+      <c r="CP13" t="inlineStr"/>
+      <c r="CQ13" t="inlineStr"/>
+      <c r="CR13" t="inlineStr"/>
+      <c r="CS13" t="inlineStr"/>
+      <c r="CT13" t="inlineStr"/>
+      <c r="CU13" t="inlineStr"/>
+      <c r="CV13" t="inlineStr"/>
+      <c r="CW13" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="CX13" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ13" t="inlineStr">
+        <is>
+          <t>100A</t>
+        </is>
+      </c>
+      <c r="DA13" t="inlineStr">
+        <is>
+          <t>열배관</t>
+        </is>
+      </c>
+      <c r="DB13" t="inlineStr"/>
+      <c r="DC13" t="inlineStr"/>
+      <c r="DD13" t="inlineStr"/>
+      <c r="DE13" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/home/src/site_apps/central/data/Material_Inventory.xlsx
+++ b/home/src/site_apps/central/data/Material_Inventory.xlsx
@@ -21,9 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -54,9 +56,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -21424,7 +21427,7 @@
         <v>10</v>
       </c>
       <c r="S406" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="407">
@@ -24596,7 +24599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24778,6 +24781,116 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B3" t="n">
+        <v>406</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-60</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>중앙지사 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>부장 주진철, 차장 권인경</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>중앙지사</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>81두1580 (탑차)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B4" t="n">
+        <v>406</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-54</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>중앙지사 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>부장 주진철, 차장 권인경</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>중앙지사</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24841,7 +24954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DE13"/>
+  <dimension ref="A1:DE15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28535,6 +28648,534 @@
         <v>0</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>중앙지사</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>406</v>
+      </c>
+      <c r="D14" t="n">
+        <v>60</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" s="1" t="n">
+        <v>46302.44401229166</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Se-75</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>205412</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>12324720</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일08:00</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>50,000</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>차장 권인경</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일08:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>50,000</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>81두1580 (탑차)</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>한국지역난방공사 중앙지사</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr"/>
+      <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="inlineStr"/>
+      <c r="BR14" t="inlineStr"/>
+      <c r="BS14" t="inlineStr"/>
+      <c r="BT14" t="inlineStr"/>
+      <c r="BU14" t="inlineStr"/>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>Pipe</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr"/>
+      <c r="BX14" t="inlineStr"/>
+      <c r="BY14" t="inlineStr"/>
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr"/>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>야간</t>
+        </is>
+      </c>
+      <c r="CC14" t="inlineStr">
+        <is>
+          <t>Ir-192 또는 Se-75 (1.0)</t>
+        </is>
+      </c>
+      <c r="CD14" t="inlineStr">
+        <is>
+          <t>15mm 이하 (1.0)</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr"/>
+      <c r="CF14" t="inlineStr"/>
+      <c r="CG14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>60</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>556440</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>4669980</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>5136960</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>1961340</v>
+      </c>
+      <c r="CM14" t="inlineStr"/>
+      <c r="CN14" t="inlineStr"/>
+      <c r="CO14" t="inlineStr"/>
+      <c r="CP14" t="inlineStr"/>
+      <c r="CQ14" t="inlineStr"/>
+      <c r="CR14" t="inlineStr"/>
+      <c r="CS14" t="inlineStr"/>
+      <c r="CT14" t="inlineStr"/>
+      <c r="CU14" t="inlineStr"/>
+      <c r="CV14" t="inlineStr"/>
+      <c r="CW14" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="CX14" t="n">
+        <v>20</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ14" t="inlineStr">
+        <is>
+          <t>100A</t>
+        </is>
+      </c>
+      <c r="DA14" t="inlineStr">
+        <is>
+          <t>열수송관</t>
+        </is>
+      </c>
+      <c r="DB14" t="inlineStr"/>
+      <c r="DC14" t="inlineStr"/>
+      <c r="DD14" t="inlineStr"/>
+      <c r="DE14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>중앙지사</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>406</v>
+      </c>
+      <c r="D15" t="n">
+        <v>54</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" s="1" t="n">
+        <v>46303.31958515822</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Se-75</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>205412</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>11092248</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일08:00</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>50,000</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>차장 권인경</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>(야간) 22:00~익일08:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>50,000</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>81두1580 (탑차)</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>한국지역난방공사 중앙지사</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr"/>
+      <c r="BP15" t="inlineStr"/>
+      <c r="BQ15" t="inlineStr"/>
+      <c r="BR15" t="inlineStr"/>
+      <c r="BS15" t="inlineStr"/>
+      <c r="BT15" t="inlineStr"/>
+      <c r="BU15" t="inlineStr"/>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>Pipe</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr"/>
+      <c r="BX15" t="inlineStr"/>
+      <c r="BY15" t="inlineStr"/>
+      <c r="BZ15" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr"/>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>야간</t>
+        </is>
+      </c>
+      <c r="CC15" t="inlineStr">
+        <is>
+          <t>Ir-192 또는 Se-75 (1.0)</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
+          <t>15mm 이하 (1.0)</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr"/>
+      <c r="CF15" t="inlineStr"/>
+      <c r="CG15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>54</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>500796</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>4202982</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>4623264</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>1765206</v>
+      </c>
+      <c r="CM15" t="inlineStr"/>
+      <c r="CN15" t="inlineStr"/>
+      <c r="CO15" t="inlineStr"/>
+      <c r="CP15" t="inlineStr"/>
+      <c r="CQ15" t="inlineStr"/>
+      <c r="CR15" t="inlineStr"/>
+      <c r="CS15" t="inlineStr"/>
+      <c r="CT15" t="inlineStr"/>
+      <c r="CU15" t="inlineStr"/>
+      <c r="CV15" t="inlineStr"/>
+      <c r="CW15" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="CX15" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="CY15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CZ15" t="inlineStr">
+        <is>
+          <t>100A</t>
+        </is>
+      </c>
+      <c r="DA15" t="inlineStr">
+        <is>
+          <t>열수송관</t>
+        </is>
+      </c>
+      <c r="DB15" t="inlineStr"/>
+      <c r="DC15" t="inlineStr"/>
+      <c r="DD15" t="inlineStr"/>
+      <c r="DE15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/home/src/site_apps/central/data/Material_Inventory.xlsx
+++ b/home/src/site_apps/central/data/Material_Inventory.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Materials" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Budget" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Settings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24875,10 +24875,26 @@
           <t>중앙지사</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>81두1580 (탑차)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -24954,7 +24970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DE15"/>
+  <dimension ref="A1:DE16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28912,7 +28928,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>46302</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -28928,7 +28944,7 @@
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" s="1" t="n">
-        <v>46303.31958515822</v>
+        <v>46303.31958516204</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -29151,15 +29167,11 @@
           <t>ORI</t>
         </is>
       </c>
-      <c r="CX15" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="CY15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="CX15" t="n">
+        <v>18</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0</v>
       </c>
       <c r="CZ15" t="inlineStr">
         <is>
@@ -29174,7 +29186,248 @@
       <c r="DB15" t="inlineStr"/>
       <c r="DC15" t="inlineStr"/>
       <c r="DD15" t="inlineStr"/>
-      <c r="DE15" t="inlineStr"/>
+      <c r="DE15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>중앙지사</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>0.8784</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" s="1" t="n">
+        <v>46307.78487681138</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>0.8784</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>75433</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>66260</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>(주간) 09:00~18:00</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>91주8839 (스타렉스)</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:안함|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:안함</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>한국지역난방공사 중앙지사</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr"/>
+      <c r="BP16" t="inlineStr"/>
+      <c r="BQ16" t="inlineStr"/>
+      <c r="BR16" t="inlineStr"/>
+      <c r="BS16" t="inlineStr"/>
+      <c r="BT16" t="inlineStr"/>
+      <c r="BU16" t="inlineStr"/>
+      <c r="BV16" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BW16" t="inlineStr"/>
+      <c r="BX16" t="inlineStr"/>
+      <c r="BY16" t="inlineStr"/>
+      <c r="BZ16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="CA16" t="inlineStr"/>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="CC16" t="inlineStr">
+        <is>
+          <t>조건없음 (1.0)</t>
+        </is>
+      </c>
+      <c r="CD16" t="inlineStr"/>
+      <c r="CE16" t="inlineStr"/>
+      <c r="CF16" t="inlineStr"/>
+      <c r="CG16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0.8784</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>361</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>26150</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>28765</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>10982</v>
+      </c>
+      <c r="CM16" t="inlineStr"/>
+      <c r="CN16" t="inlineStr"/>
+      <c r="CO16" t="inlineStr"/>
+      <c r="CP16" t="inlineStr"/>
+      <c r="CQ16" t="inlineStr"/>
+      <c r="CR16" t="inlineStr"/>
+      <c r="CS16" t="inlineStr"/>
+      <c r="CT16" t="inlineStr"/>
+      <c r="CU16" t="inlineStr"/>
+      <c r="CV16" t="inlineStr"/>
+      <c r="CW16" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="CX16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="CY16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CZ16" t="inlineStr">
+        <is>
+          <t>125A</t>
+        </is>
+      </c>
+      <c r="DA16" t="inlineStr">
+        <is>
+          <t>열수송관</t>
+        </is>
+      </c>
+      <c r="DB16" t="inlineStr"/>
+      <c r="DC16" t="inlineStr"/>
+      <c r="DD16" t="inlineStr"/>
+      <c r="DE16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
